--- a/data/Resultados_finales_tesis/Mina_modelo/P_red/elmo_data.xlsx
+++ b/data/Resultados_finales_tesis/Mina_modelo/P_red/elmo_data.xlsx
@@ -3567,7 +3567,7 @@
         <v>0.8</v>
       </c>
       <c r="E3" s="23" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
